--- a/Data Files/10.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
+++ b/Data Files/10.1. Credit Transfer - Success Partisipan Debitur ke Partisipan Kreditur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE77EA0-77F8-4A9D-825F-12FCD655095A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EE5CD6-4C64-443E-B2D2-9AF51A5C2D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
@@ -207,7 +207,7 @@
     <t>LclInstrmPrtry</t>
   </si>
   <si>
-    <t>20250424PDJBIDJA01000014681</t>
+    <t>20250424PDJBIDJA01000014682</t>
   </si>
 </sst>
 </file>
@@ -294,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -303,8 +303,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,52 +788,52 @@
       <c r="Q2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="X2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="9" t="s">
+      <c r="Y2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="Z2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AC2" s="9" t="s">
+      <c r="AC2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="9" t="s">
+      <c r="AD2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AE2" s="9" t="s">
+      <c r="AE2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AF2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AG2" s="4" t="s">
         <v>58</v>
       </c>
     </row>
